--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_arica_y_parinacota.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_arica_y_parinacota.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -417,7 +417,7 @@
         <v>0.8132676120106153</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -444,7 +444,7 @@
         <v>14.85321686581045</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -471,13 +471,13 @@
         <v>9.170187343182622</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -486,25 +486,25 @@
         </is>
       </c>
       <c r="C5">
-        <v>278197.94</v>
+        <v>277508.94</v>
       </c>
       <c r="D5">
-        <v>248490.89</v>
+        <v>247977.25</v>
       </c>
       <c r="E5">
-        <v>29707.04999999999</v>
+        <v>29531.69</v>
       </c>
       <c r="F5">
-        <v>11.9549855529915</v>
+        <v>11.90903197773183</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -513,45 +513,126 @@
         </is>
       </c>
       <c r="C6">
-        <v>457087.19</v>
+        <v>455872.97</v>
       </c>
       <c r="D6">
-        <v>418743.91</v>
+        <v>417522.69</v>
       </c>
       <c r="E6">
-        <v>38343.28000000003</v>
+        <v>38350.27999999997</v>
       </c>
       <c r="F6">
-        <v>9.156737348132427</v>
+        <v>9.185196617697589</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>366089.97</v>
+      </c>
+      <c r="D7">
+        <v>332491.41</v>
+      </c>
+      <c r="E7">
+        <v>33598.56</v>
+      </c>
+      <c r="F7">
+        <v>10.10509113603868</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Arica</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>278197.94</v>
+      </c>
+      <c r="D8">
+        <v>248490.89</v>
+      </c>
+      <c r="E8">
+        <v>29707.04999999999</v>
+      </c>
+      <c r="F8">
+        <v>11.9549855529915</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>457087.19</v>
+      </c>
+      <c r="D9">
+        <v>418743.91</v>
+      </c>
+      <c r="E9">
+        <v>38343.28000000003</v>
+      </c>
+      <c r="F9">
+        <v>9.156737348132427</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7">
+      <c r="C10">
         <v>367015.34</v>
       </c>
-      <c r="D7">
+      <c r="D10">
         <v>333330.72</v>
       </c>
-      <c r="E7">
+      <c r="E10">
         <v>33684.62000000005</v>
       </c>
-      <c r="F7">
+      <c r="F10">
         <v>10.10546522684739</v>
       </c>
-      <c r="G7">
+      <c r="G10">
         <v>1</v>
       </c>
     </row>
@@ -604,7 +685,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -737,6 +818,60 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>332491.41</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>366089.97</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>379913.69</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_arica_y_parinacota.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_arica_y_parinacota.xlsx
@@ -1,48 +1,151 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="barras" sheetId="1" r:id="rId1"/>
-    <sheet name="mapa" sheetId="2" r:id="rId2"/>
-    <sheet name="serie" sheetId="3" r:id="rId3"/>
+    <sheet name="Barras" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Mapa" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Serie" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Serie'!$A$1:$C$10</definedName>
+  </definedNames>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t xml:space="preserve">Provincia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subgrupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valor_prev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">delta_pp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">delta_pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prov_rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parinacota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Femenino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masculino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promedio Regional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de creación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27 22:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIT - MDSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagen asociada</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valor_hist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00135A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,21 +153,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -114,10 +233,6 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -143,15 +258,12 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -177,6 +289,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -352,527 +465,490 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>subgrupo</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>valor_prev</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>delta_pp</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>delta_pct</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>prov_rank</t>
-        </is>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Parinacota</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="C2">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>168736.62</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2" t="n">
         <v>167375.41</v>
       </c>
-      <c r="E2">
-        <v>1361.209999999992</v>
-      </c>
-      <c r="F2">
-        <v>0.8132676120106153</v>
-      </c>
-      <c r="G2">
+      <c r="E2" s="2" t="n">
+        <v>1361.21</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Parinacota</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="C3">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>279516.62</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2" t="n">
         <v>243368.56</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2" t="n">
         <v>36148.06</v>
       </c>
-      <c r="F3">
-        <v>14.85321686581045</v>
-      </c>
-      <c r="G3">
+      <c r="F3" s="2" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Parinacota</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C4">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>226047.91</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2" t="n">
         <v>207060.11</v>
       </c>
-      <c r="E4">
-        <v>18987.80000000002</v>
-      </c>
-      <c r="F4">
-        <v>9.170187343182622</v>
-      </c>
-      <c r="G4">
+      <c r="E4" s="2" t="n">
+        <v>18987.8</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Promedio Regional</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="C5">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>277508.94</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2" t="n">
         <v>247977.25</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2" t="n">
         <v>29531.69</v>
       </c>
-      <c r="F5">
-        <v>11.90903197773183</v>
-      </c>
-      <c r="G5">
+      <c r="F5" s="2" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Promedio Regional</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="C6">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>455872.97</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2" t="n">
         <v>417522.69</v>
       </c>
-      <c r="E6">
-        <v>38350.27999999997</v>
-      </c>
-      <c r="F6">
-        <v>9.185196617697589</v>
-      </c>
-      <c r="G6">
+      <c r="E6" s="2" t="n">
+        <v>38350.28</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Promedio Regional</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C7">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>366089.97</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2" t="n">
         <v>332491.41</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2" t="n">
         <v>33598.56</v>
       </c>
-      <c r="F7">
-        <v>10.10509113603868</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="2" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="C8">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>278197.94</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2" t="n">
         <v>248490.89</v>
       </c>
-      <c r="E8">
-        <v>29707.04999999999</v>
-      </c>
-      <c r="F8">
-        <v>11.9549855529915</v>
-      </c>
-      <c r="G8">
+      <c r="E8" s="2" t="n">
+        <v>29707.05</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="C9">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="n">
         <v>457087.19</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2" t="n">
         <v>418743.91</v>
       </c>
-      <c r="E9">
-        <v>38343.28000000003</v>
-      </c>
-      <c r="F9">
-        <v>9.156737348132427</v>
-      </c>
-      <c r="G9">
+      <c r="E9" s="2" t="n">
+        <v>38343.28</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C10">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="n">
         <v>367015.34</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2" t="n">
         <v>333330.72</v>
       </c>
-      <c r="E10">
-        <v>33684.62000000005</v>
-      </c>
-      <c r="F10">
-        <v>10.10546522684739</v>
-      </c>
-      <c r="G10">
+      <c r="E10" s="2" t="n">
+        <v>33684.62</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="G10" s="2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G10"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="60.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>367015.34</v>
+      <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Parinacota</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>226047.91</v>
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>valor_hist</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>is_cur</t>
-        </is>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C2">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>367015.34</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>226047.91</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="19.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>333330.72</v>
       </c>
-      <c r="D2" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C3">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>367015.34</v>
       </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Arica</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C4">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2" t="n">
         <v>380768.84</v>
       </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Parinacota</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C5">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>207060.11</v>
       </c>
-      <c r="D5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Parinacota</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C6">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>226047.91</v>
       </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Parinacota</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C7">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>250484.62</v>
       </c>
-      <c r="D7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Promedio Regional</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C8">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>332491.41</v>
       </c>
-      <c r="D8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Promedio Regional</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C9">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2" t="n">
         <v>366089.97</v>
       </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Promedio Regional</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C10">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="2" t="n">
         <v>379913.69</v>
       </c>
-      <c r="D10" t="b">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C10"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_arica_y_parinacota.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_arica_y_parinacota.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t xml:space="preserve">Provincia</t>
   </si>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:08</t>
+    <t xml:space="preserve">2026-08-19 14:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -80,13 +80,19 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">prov_i_ingr_mean_a_2023_arica_y_parinacota.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingreso de la población en edad de trabajar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region de Arica y Parinacota</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -761,23 +767,23 @@
         <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -800,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
@@ -841,10 +847,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
@@ -852,7 +858,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>333330.72</v>
@@ -863,7 +869,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>367015.34</v>
@@ -874,7 +880,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>380768.84</v>
@@ -885,7 +891,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>207060.11</v>
@@ -896,7 +902,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>226047.91</v>
@@ -907,7 +913,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>250484.62</v>
@@ -918,7 +924,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>332491.41</v>
@@ -929,7 +935,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>366089.97</v>
@@ -940,7 +946,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>379913.69</v>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_arica_y_parinacota.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_arica_y_parinacota.xlsx
@@ -68,7 +68,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 14:24</t>
+    <t xml:space="preserve">2026-09-07 11:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
